--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0003T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0003T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>71.19813307088748</v>
+        <v>11.56969662401922</v>
       </c>
       <c r="D2" t="n">
-        <v>71.75674785832824</v>
+        <v>11.66047152697834</v>
       </c>
       <c r="E2" t="n">
-        <v>7.623581703842533</v>
+        <v>1.238832026874412</v>
       </c>
       <c r="F2" t="n">
-        <v>7.639078860447619</v>
+        <v>1.241350314822738</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>80.57010142233729</v>
+        <v>13.09264148112981</v>
       </c>
       <c r="D3" t="n">
-        <v>81.11156772470405</v>
+        <v>13.18062975526441</v>
       </c>
       <c r="E3" t="n">
-        <v>7.623581703842533</v>
+        <v>1.238832026874412</v>
       </c>
       <c r="F3" t="n">
-        <v>7.639078860447619</v>
+        <v>1.241350314822738</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>89.87197440533399</v>
+        <v>14.60419584086677</v>
       </c>
       <c r="D4" t="n">
-        <v>90.46859312797928</v>
+        <v>14.70114638329663</v>
       </c>
       <c r="E4" t="n">
-        <v>7.623581703842533</v>
+        <v>1.238832026874412</v>
       </c>
       <c r="F4" t="n">
-        <v>7.639078860447619</v>
+        <v>1.241350314822738</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
